--- a/db_nilai.xlsx
+++ b/db_nilai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thinkpad\Downloads\sistem-penilaian-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thinkpad\OneDrive\Documents\WEBSITE\pacpnkemang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1941748-22B3-46EF-B285-19620FA0F114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6779E95-CB12-46BC-A76D-A88AFD8DCB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{C90172FA-9549-4883-B5C1-C1958433D4C2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Kelompok</t>
   </si>
@@ -42,71 +42,26 @@
     <t>Nama</t>
   </si>
   <si>
-    <t>DEPISKA DWI PEBRIANI</t>
+    <t>Dwi Nur Aini</t>
   </si>
   <si>
-    <t>ANGGI ANGRAENI</t>
+    <t>Dede Ahmad Fauzan</t>
   </si>
   <si>
-    <t>SITI RAHMA PRIATI</t>
+    <t>Hoirul Sambudi</t>
   </si>
   <si>
-    <t>SITI NURJANAH</t>
+    <t>Rendi Imam Saputra</t>
   </si>
   <si>
-    <t>ANNISA QOTRUN NADA</t>
-  </si>
-  <si>
-    <t>ZAHRA NAYNAWA</t>
-  </si>
-  <si>
-    <t>ABDUL FIKAR PURNOMO</t>
-  </si>
-  <si>
-    <t>EVA LISTIANA</t>
-  </si>
-  <si>
-    <t>AMMAR ABDURRAHMAN AZIZ</t>
-  </si>
-  <si>
-    <t>SYAFIQ ABQORI AFHAM</t>
-  </si>
-  <si>
-    <t>FAKHRI ADIS FADHILAH</t>
-  </si>
-  <si>
-    <t>AHDU SYAKBAN KHOIRSYAH</t>
-  </si>
-  <si>
-    <t>M. HUSAIN AMIRUDDIN</t>
-  </si>
-  <si>
-    <t>MUHAMMAD QASHMAL QADUMI</t>
-  </si>
-  <si>
-    <t>DIYANTI SEKAR ARUM</t>
-  </si>
-  <si>
-    <t>RISNA</t>
-  </si>
-  <si>
-    <t>FATHMA ANNYSHA</t>
-  </si>
-  <si>
-    <t>KHALISHA</t>
-  </si>
-  <si>
-    <t>AHMAD AZARRUDDIN</t>
-  </si>
-  <si>
-    <t>MUHAMMAD GIOVANO GIBRAN P.</t>
+    <t>Fatma Nabila Lutfiana</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +92,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -146,7 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -154,11 +115,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -181,6 +157,9 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,7 +491,7 @@
     <col min="12" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,30 +501,30 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>20</v>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
+      <c r="B3" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
+      <c r="B4" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="E4" s="5"/>
       <c r="G4" s="6"/>
@@ -553,155 +532,92 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>16</v>
+      <c r="B5" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
+      <c r="B7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="B9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="8">
-        <v>3</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="8">
-        <v>3</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
-        <v>3</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="8">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="B15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
-        <v>4</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="4"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="8">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="4"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <v>5</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="5"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
-        <v>5</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
-        <v>5</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A21" s="8"/>
+      <c r="B21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/db_nilai.xlsx
+++ b/db_nilai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thinkpad\OneDrive\Documents\WEBSITE\pacpnkemang\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thinkpad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6779E95-CB12-46BC-A76D-A88AFD8DCB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D4AE6E-8B7E-4146-9BDC-49406541C9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{C90172FA-9549-4883-B5C1-C1958433D4C2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Kelompok</t>
   </si>
@@ -55,13 +55,49 @@
   </si>
   <si>
     <t>Fatma Nabila Lutfiana</t>
+  </si>
+  <si>
+    <t>Wilda Nazwatun Nisa</t>
+  </si>
+  <si>
+    <t>Khairun Anwar</t>
+  </si>
+  <si>
+    <t>Dinda Ayuni</t>
+  </si>
+  <si>
+    <t>Nurul Hidayah Harahap</t>
+  </si>
+  <si>
+    <t>Syahrul Mubarok</t>
+  </si>
+  <si>
+    <t>Agung Prayuda</t>
+  </si>
+  <si>
+    <t>Mochammad Wafi Nur Jihan</t>
+  </si>
+  <si>
+    <t>Citra Hayatunnufus</t>
+  </si>
+  <si>
+    <t>Naufal Maulana Widodo</t>
+  </si>
+  <si>
+    <t>Ardan Mizanul Khoiri</t>
+  </si>
+  <si>
+    <t>Ramlan</t>
+  </si>
+  <si>
+    <t>Muhammad Ramadhan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,12 +128,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -107,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -115,26 +145,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -157,9 +172,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,7 +503,7 @@
     <col min="12" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,30 +513,30 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>2</v>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>4</v>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="5"/>
       <c r="G4" s="6"/>
@@ -532,79 +544,130 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="5"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="8"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="2">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="8"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="8"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="2">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="8"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="2">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="8"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="2">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
